--- a/TestData/LV_1_CF_TMTT0049771_VerifyMergersAcquisitionsMAChangesInOpportunityCreationToEngagementConversionWithTheApprovalProcess.xlsx
+++ b/TestData/LV_1_CF_TMTT0049771_VerifyMergersAcquisitionsMAChangesInOpportunityCreationToEngagementConversionWithTheApprovalProcess.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77E5EF47-3E97-44FC-AAF2-BE15F8CFC47D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE1C4F7-2962-430D-A144-EC98696A8A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUsers" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="115">
   <si>
     <t>James Craven</t>
   </si>
@@ -250,9 +250,6 @@
     <t>Kristian M. Whalen</t>
   </si>
   <si>
-    <t>Buyside</t>
-  </si>
-  <si>
     <t>Sellside</t>
   </si>
   <si>
@@ -265,12 +262,6 @@
     <t>Engagements</t>
   </si>
   <si>
-    <t>Legal User</t>
-  </si>
-  <si>
-    <t>Christine Sha</t>
-  </si>
-  <si>
     <t>Legal Hold test Notes</t>
   </si>
   <si>
@@ -337,9 +328,6 @@
     <t>Chief Operating Officer, CS</t>
   </si>
   <si>
-    <t>permission sets</t>
-  </si>
-  <si>
     <t>CAO MA</t>
   </si>
   <si>
@@ -350,6 +338,57 @@
   </si>
   <si>
     <t>CAO CS</t>
+  </si>
+  <si>
+    <t>Equity Placements</t>
+  </si>
+  <si>
+    <t>Denis Collins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product Speiality </t>
+  </si>
+  <si>
+    <t>CS</t>
+  </si>
+  <si>
+    <t>M&amp;A</t>
+  </si>
+  <si>
+    <t>Capital Solutions</t>
+  </si>
+  <si>
+    <t>Conversion CF CS</t>
+  </si>
+  <si>
+    <t>Compliance User</t>
+  </si>
+  <si>
+    <t>Administrative Coordinator - Compliance</t>
+  </si>
+  <si>
+    <t>DND Approval</t>
+  </si>
+  <si>
+    <t>DND ON&amp; OFF</t>
+  </si>
+  <si>
+    <t>Permission sets</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>DNDAssignedTo</t>
+  </si>
+  <si>
+    <t>DNDActualApprover</t>
+  </si>
+  <si>
+    <t>DND Approval Q</t>
+  </si>
+  <si>
+    <t>Justus Seyler</t>
   </si>
 </sst>
 </file>
@@ -1074,27 +1113,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1109,7 +1165,7 @@
   <cols>
     <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
@@ -1122,63 +1178,72 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" t="s">
         <v>94</v>
       </c>
-      <c r="D2" t="s">
-        <v>98</v>
-      </c>
       <c r="E2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E3" t="s">
         <v>96</v>
-      </c>
-      <c r="D3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E3" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>105</v>
+      </c>
+      <c r="C5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E5" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1229,7 +1294,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1260,7 +1325,7 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>13</v>
@@ -1349,10 +1414,10 @@
         <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
         <v>40</v>
@@ -1441,10 +1506,10 @@
         <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
         <v>40</v>
@@ -1623,10 +1688,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -1634,10 +1699,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1651,7 +1716,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCF8D60A-1002-4D00-B235-C15EB6546928}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
@@ -1659,75 +1724,104 @@
     <col min="3" max="4" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="H2" t="s">
+        <v>110</v>
+      </c>
+      <c r="I2" t="s">
+        <v>113</v>
+      </c>
+      <c r="J2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="F2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>92</v>
+      <c r="H3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J3" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -1745,12 +1839,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
